--- a/data/trans_orig/P23_1_2016_2023_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84737</t>
+          <t>85123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120785</t>
+          <t>121177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54320</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85729</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149629</t>
+          <t>149174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196424</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308307</t>
+          <t>307915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344355</t>
+          <t>343969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261326</t>
+          <t>262357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292735</t>
+          <t>292937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579723</t>
+          <t>581665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>626518</t>
+          <t>626973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69306</t>
+          <t>68901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101675</t>
+          <t>101743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134362</t>
+          <t>132658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180469</t>
+          <t>178843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274480</t>
+          <t>274412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306849</t>
+          <t>307254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284666</t>
+          <t>282668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315355</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>566932</t>
+          <t>568558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>613039</t>
+          <t>614743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>99205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135791</t>
+          <t>137937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115862</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157178</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386123</t>
+          <t>383977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422705</t>
+          <t>422709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140567</t>
+          <t>140307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156112</t>
+          <t>156740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530858</t>
+          <t>530762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>572174</t>
+          <t>573540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>236122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295514</t>
+          <t>294422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121607</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>328487</t>
+          <t>330204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397852</t>
+          <t>398462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853260</t>
+          <t>854352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>911715</t>
+          <t>912652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>703341</t>
+          <t>702270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741932</t>
+          <t>742912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1575870</t>
+          <t>1575260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1645235</t>
+          <t>1643518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>107892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149343</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>101886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>184210</t>
+          <t>185429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>237033</t>
+          <t>240435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471363</t>
+          <t>471061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>511314</t>
+          <t>512814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635469</t>
+          <t>635269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670112</t>
+          <t>670110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1120828</t>
+          <t>1117426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1173651</t>
+          <t>1172432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>68023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274233</t>
+          <t>275319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285030</t>
+          <t>285031</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1017497</t>
+          <t>1017263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1044882</t>
+          <t>1044884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1299047</t>
+          <t>1298752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1328870</t>
+          <t>1327044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>658055</t>
+          <t>653910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>758039</t>
+          <t>751744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>347008</t>
+          <t>349214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>423988</t>
+          <t>425286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1027897</t>
+          <t>1030969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151777</t>
+          <t>1151360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2625746</t>
+          <t>2632041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2725730</t>
+          <t>2729875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3102169</t>
+          <t>3100871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3179149</t>
+          <t>3176943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5758166</t>
+          <t>5758583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5882046</t>
+          <t>5878974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105421</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144252</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79351</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>164782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212008</t>
+          <t>212982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360960</t>
+          <t>360110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399791</t>
+          <t>400010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368116</t>
+          <t>370197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393171</t>
+          <t>394335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740671</t>
+          <t>739697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>786820</t>
+          <t>787897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78715</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>111291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69837</t>
+          <t>69312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130467</t>
+          <t>130927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170116</t>
+          <t>172080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341496</t>
+          <t>340922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373498</t>
+          <t>374645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312743</t>
+          <t>313268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336775</t>
+          <t>336918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664677</t>
+          <t>662713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704326</t>
+          <t>703866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145699</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>549616</t>
+          <t>534936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158986</t>
+          <t>159355</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>637395</t>
+          <t>614633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118648</t>
+          <t>133328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522565</t>
+          <t>525349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137066</t>
+          <t>137488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151077</t>
+          <t>151283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197780</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>676189</t>
+          <t>675820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167095</t>
+          <t>166445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213611</t>
+          <t>214773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185504</t>
+          <t>182589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310813</t>
+          <t>312362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821208</t>
+          <t>820046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867724</t>
+          <t>868374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>874179</t>
+          <t>871891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938228</t>
+          <t>935087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1701437</t>
+          <t>1699888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826746</t>
+          <t>1829661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73643</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>107417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130292</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185427</t>
+          <t>183253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368404</t>
+          <t>366599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400373</t>
+          <t>400358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>752859</t>
+          <t>751088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>789628</t>
+          <t>787853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129243</t>
+          <t>1131417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1184378</t>
+          <t>1184536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>49088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58187</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223225</t>
+          <t>223353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237096</t>
+          <t>236984</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711185</t>
+          <t>712283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>732836</t>
+          <t>733243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>942688</t>
+          <t>941121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>966930</t>
+          <t>966372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>632146</t>
+          <t>633550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1411059</t>
+          <t>1579480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>268219</t>
+          <t>275929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368295</t>
+          <t>371422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>940369</t>
+          <t>939241</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2024794</t>
+          <t>1947035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1962969</t>
+          <t>1794548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2741882</t>
+          <t>2740478</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3208119</t>
+          <t>3204992</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3308195</t>
+          <t>3300485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4925647</t>
+          <t>5003406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6010072</t>
+          <t>6011200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>85299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>85451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149174</t>
+          <t>146196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194482</t>
+          <t>196092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307915</t>
+          <t>305497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343969</t>
+          <t>343793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262357</t>
+          <t>261604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292937</t>
+          <t>293735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>581665</t>
+          <t>580055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>626973</t>
+          <t>629951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101743</t>
+          <t>102901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>133569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178843</t>
+          <t>177709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274412</t>
+          <t>273254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307254</t>
+          <t>306933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282668</t>
+          <t>284961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316268</t>
+          <t>315223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568558</t>
+          <t>569692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>614743</t>
+          <t>613832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99205</t>
+          <t>98446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137937</t>
+          <t>140139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>114280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157274</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383977</t>
+          <t>381775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422709</t>
+          <t>423468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140307</t>
+          <t>139885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156740</t>
+          <t>156310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530762</t>
+          <t>532040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573540</t>
+          <t>573756</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236122</t>
+          <t>235052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294422</t>
+          <t>295426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>80907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122678</t>
+          <t>119332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330204</t>
+          <t>329026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398462</t>
+          <t>404296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854352</t>
+          <t>853348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>912652</t>
+          <t>913722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702270</t>
+          <t>705616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742912</t>
+          <t>744041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1575260</t>
+          <t>1569426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1643518</t>
+          <t>1644696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149645</t>
+          <t>148701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185429</t>
+          <t>185629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240435</t>
+          <t>239334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471061</t>
+          <t>472005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>512814</t>
+          <t>512250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635269</t>
+          <t>634969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670110</t>
+          <t>670264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1117426</t>
+          <t>1118527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1172432</t>
+          <t>1172232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>40395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68023</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275319</t>
+          <t>275129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285031</t>
+          <t>285034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1017263</t>
+          <t>1017702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1044884</t>
+          <t>1045028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298752</t>
+          <t>1296327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1327044</t>
+          <t>1326380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>653910</t>
+          <t>661764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>751744</t>
+          <t>759549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>349214</t>
+          <t>352023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>428245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1030969</t>
+          <t>1026421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151360</t>
+          <t>1144408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2632041</t>
+          <t>2624236</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2729875</t>
+          <t>2722021</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3100871</t>
+          <t>3097912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3176943</t>
+          <t>3174134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5758583</t>
+          <t>5765535</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5878974</t>
+          <t>5883522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>123377</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>108770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145102</t>
+          <t>149858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>83326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164782</t>
+          <t>176732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212982</t>
+          <t>226570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>381835</t>
+          <t>419998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360110</t>
+          <t>400760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400010</t>
+          <t>441848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>382436</t>
+          <t>418986</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>405085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394335</t>
+          <t>430865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>764271</t>
+          <t>838985</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739697</t>
+          <t>812459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>787897</t>
+          <t>862297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>86744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111291</t>
+          <t>121212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69312</t>
+          <t>76383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130927</t>
+          <t>144080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172080</t>
+          <t>187900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>358927</t>
+          <t>380861</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340922</t>
+          <t>362000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374645</t>
+          <t>396468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>325859</t>
+          <t>360307</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313268</t>
+          <t>346760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336918</t>
+          <t>372466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>684786</t>
+          <t>741167</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662713</t>
+          <t>718455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703866</t>
+          <t>762275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,1%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>340616</t>
+          <t>106179</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142915</t>
+          <t>88738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>534936</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>362424</t>
+          <t>128860</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159355</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>614633</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>327648</t>
+          <t>365433</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133328</t>
+          <t>348222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525349</t>
+          <t>382874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>145103</t>
+          <t>164815</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137488</t>
+          <t>156742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151283</t>
+          <t>171766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>472751</t>
+          <t>530249</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220542</t>
+          <t>509464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675820</t>
+          <t>548726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>190253</t>
+          <t>212025</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166445</t>
+          <t>187074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214773</t>
+          <t>238504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>269231</t>
+          <t>297136</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182589</t>
+          <t>270114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312362</t>
+          <t>330929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>844566</t>
+          <t>919818</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>820046</t>
+          <t>893339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868374</t>
+          <t>944769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>898454</t>
+          <t>775398</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871891</t>
+          <t>759310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>935087</t>
+          <t>790264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1743019</t>
+          <t>1695216</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1699888</t>
+          <t>1661423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829661</t>
+          <t>1722238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88896</t>
+          <t>95144</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73658</t>
+          <t>78994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107417</t>
+          <t>115122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70710</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89566</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>159606</t>
+          <t>175612</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130134</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183253</t>
+          <t>197412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>385120</t>
+          <t>471738</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366599</t>
+          <t>451760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400358</t>
+          <t>487888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>769944</t>
+          <t>749677</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751088</t>
+          <t>733347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>787853</t>
+          <t>763082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1155064</t>
+          <t>1221414</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1131417</t>
+          <t>1199614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1184536</t>
+          <t>1242588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>29304</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49088</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232526</t>
+          <t>229420</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223353</t>
+          <t>221324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236984</t>
+          <t>233638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>724117</t>
+          <t>806114</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>712283</t>
+          <t>794647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>733243</t>
+          <t>814977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>956643</t>
+          <t>1035534</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941121</t>
+          <t>1022311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>966372</t>
+          <t>1045822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>843407</t>
+          <t>652984</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>633550</t>
+          <t>610113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1579480</t>
+          <t>702416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>330501</t>
+          <t>358689</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275929</t>
+          <t>326121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>371422</t>
+          <t>390970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1173908</t>
+          <t>1011673</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>939241</t>
+          <t>956653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1947035</t>
+          <t>1064724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2530621</t>
+          <t>2787268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1794548</t>
+          <t>2737836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2740478</t>
+          <t>2830139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3245913</t>
+          <t>3275296</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3204992</t>
+          <t>3243015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3300485</t>
+          <t>3307864</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5776533</t>
+          <t>6062564</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5003406</t>
+          <t>6009513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6011200</t>
+          <t>6117584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
